--- a/product_selector_out/STM32G4x4 - diff.xlsx
+++ b/product_selector_out/STM32G4x4 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -66,13 +71,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -541,7 +547,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -611,7 +617,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1488</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="18">
@@ -649,18 +655,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -672,16 +682,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -690,21 +700,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32G474QB</t>
+          <t>STM32G474CB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -718,16 +728,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -736,21 +746,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32G474VE</t>
+          <t>STM32G474QB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -764,16 +774,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -782,21 +792,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32G474VC</t>
+          <t>STM32G474VE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -810,16 +820,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -828,21 +838,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32G474VB</t>
+          <t>STM32G474VC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -856,16 +866,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -874,21 +884,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32G484QE</t>
+          <t>STM32G474VB</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -902,16 +912,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -920,21 +930,21 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32G474ME</t>
+          <t>STM32G484QE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -948,16 +958,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -966,21 +976,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32G484VE</t>
+          <t>STM32G474ME</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -994,16 +1004,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1012,21 +1022,21 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32G474RE</t>
+          <t>STM32G484VE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1040,16 +1050,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1058,21 +1068,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32G474PC</t>
+          <t>STM32G474RE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1086,16 +1096,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1104,21 +1114,21 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32G484ME</t>
+          <t>STM32G474PC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1132,16 +1142,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1150,21 +1160,21 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32G474RC</t>
+          <t>STM32G484ME</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1178,16 +1188,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1196,21 +1206,21 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32G474MC</t>
+          <t>STM32G474RC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1224,16 +1234,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1242,21 +1252,21 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32G474MB</t>
+          <t>STM32G474MC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1270,16 +1280,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1288,21 +1298,21 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32G484RE</t>
+          <t>STM32G474MB</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1316,16 +1326,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1334,21 +1344,21 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32G474RB</t>
+          <t>STM32G484RE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1362,16 +1372,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1380,21 +1390,21 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32G484CE</t>
+          <t>STM32G474RB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1408,16 +1418,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1426,21 +1436,21 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32G474CE</t>
+          <t>STM32G484CE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1454,25 +1464,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32G474QE</t>
+          <t>STM32G474CE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1486,7 +1500,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1495,7 +1509,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32G474QE</t>
+          <t>STM32G474CE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1509,7 +1523,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1518,7 +1532,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32G474CC</t>
+          <t>STM32G474QE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1532,7 +1546,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1541,7 +1555,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32G474CC</t>
+          <t>STM32G474QE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1555,7 +1569,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1564,44 +1578,48 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32G474QC</t>
+          <t>STM32G474CC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32G474QC</t>
+          <t>STM32G474CC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1610,21 +1628,21 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32G474PE</t>
+          <t>STM32G474CC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1633,21 +1651,21 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32G474PE</t>
+          <t>STM32G474QC</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1656,21 +1674,21 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32G474PB</t>
+          <t>STM32G474QC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1679,21 +1697,21 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32G474PB</t>
+          <t>STM32G474PE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1702,21 +1720,21 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32G484PE</t>
+          <t>STM32G474PE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1725,28 +1743,97 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32G484PE</t>
+          <t>STM32G474PB</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>STM32G474PB</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>STM32G484PE</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>STM32G484PE</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E66"/>
+  <autoFilter ref="A18:E69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32G4x4 - diff.xlsx
+++ b/product_selector_out/STM32G4x4 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1536</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1485</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="18">
@@ -723,18 +723,18 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32G474QB</t>
+          <t>STM32G474CB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -751,13 +751,13 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -769,18 +769,18 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32G474VE</t>
+          <t>STM32G474QB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -792,18 +792,18 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32G474VE</t>
+          <t>STM32G474QB</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32G474VC</t>
+          <t>STM32G474VE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -838,7 +838,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32G474VC</t>
+          <t>STM32G474VE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -861,18 +861,18 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32G474VB</t>
+          <t>STM32G474VE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -884,18 +884,18 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32G474VB</t>
+          <t>STM32G474VC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -907,18 +907,18 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32G484QE</t>
+          <t>STM32G474VC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -930,18 +930,18 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32G484QE</t>
+          <t>STM32G474VC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -953,7 +953,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32G474ME</t>
+          <t>STM32G474VB</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -976,7 +976,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32G474ME</t>
+          <t>STM32G474VB</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -999,18 +999,18 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32G484VE</t>
+          <t>STM32G474VB</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -1022,18 +1022,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32G484VE</t>
+          <t>STM32G484QE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -1045,18 +1045,18 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32G474RE</t>
+          <t>STM32G484QE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -1068,18 +1068,18 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32G474RE</t>
+          <t>STM32G474ME</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -1091,18 +1091,18 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32G474PC</t>
+          <t>STM32G474ME</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -1114,18 +1114,18 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32G474PC</t>
+          <t>STM32G474ME</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -1137,7 +1137,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32G484ME</t>
+          <t>STM32G484VE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1160,7 +1160,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32G484ME</t>
+          <t>STM32G484VE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1183,7 +1183,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32G474RC</t>
+          <t>STM32G474RE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1206,7 +1206,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32G474RC</t>
+          <t>STM32G474RE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1229,18 +1229,18 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32G474MC</t>
+          <t>STM32G474RE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -1252,18 +1252,18 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32G474MC</t>
+          <t>STM32G474PC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -1275,18 +1275,18 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32G474MB</t>
+          <t>STM32G474PC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -1298,18 +1298,18 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32G474MB</t>
+          <t>STM32G474PC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32G484RE</t>
+          <t>STM32G484ME</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1344,7 +1344,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32G484RE</t>
+          <t>STM32G484ME</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32G474RB</t>
+          <t>STM32G474RC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1390,7 +1390,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32G474RB</t>
+          <t>STM32G474RC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1413,18 +1413,18 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32G484CE</t>
+          <t>STM32G474RC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -1436,18 +1436,18 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32G484CE</t>
+          <t>STM32G474MC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -1459,45 +1459,41 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32G474CE</t>
+          <t>STM32G474MC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32G474CE</t>
+          <t>STM32G474MC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -1509,18 +1505,18 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32G474CE</t>
+          <t>STM32G474MB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -1532,18 +1528,18 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32G474QE</t>
+          <t>STM32G474MB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -1555,18 +1551,18 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32G474QE</t>
+          <t>STM32G474MB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -1578,45 +1574,41 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32G474CC</t>
+          <t>STM32G484RE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32G474CC</t>
+          <t>STM32G484RE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -1628,18 +1620,18 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32G474CC</t>
+          <t>STM32G474RB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -1651,18 +1643,18 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32G474QC</t>
+          <t>STM32G474RB</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -1674,18 +1666,18 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32G474QC</t>
+          <t>STM32G474RB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -1697,7 +1689,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32G474PE</t>
+          <t>STM32G484CE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1720,7 +1712,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32G474PE</t>
+          <t>STM32G484CE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1743,41 +1735,45 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32G474PB</t>
+          <t>STM32G474CE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32G474PB</t>
+          <t>STM32G474CE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -1789,18 +1785,18 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32G484PE</t>
+          <t>STM32G474CE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -1812,18 +1808,18 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32G484PE</t>
+          <t>STM32G474CE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -1832,8 +1828,426 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>STM32G474QE</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>STM32G474QE</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>STM32G474QE</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>STM32G474CC</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>STM32G474CC</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>STM32G474CC</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>STM32G474CC</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>STM32G474QC</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>STM32G474QC</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>STM32G474QC</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>STM32G474PE</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>STM32G474PE</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>STM32G474PE</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>STM32G474PB</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>STM32G474PB</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>STM32G474PB</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>STM32G484PE</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>STM32G484PE</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A18:E69"/>
+  <autoFilter ref="A18:E87"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>